--- a/KatalonData/IWPBootstrapData/NormalizedSharedData.xlsx
+++ b/KatalonData/IWPBootstrapData/NormalizedSharedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T476640\Documents\VPS_Katalon\VPS-Katalon\KatalonData\IWPBootstrapData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C57A7-7AD2-4359-B672-65423789A3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0556D7F4-54AE-48D4-A141-6516AD04314D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
   </bookViews>
   <sheets>
     <sheet name="NameData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>999999999</t>
+  </si>
+  <si>
+    <t>Carlos Jacinta</t>
   </si>
 </sst>
 </file>
@@ -678,16 +681,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4758406-EDCC-4FC2-8D56-4EE6148C26F6}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="13.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="13.7265625" style="1"/>
+    <col min="1" max="3" width="13.77734375" style="1"/>
     <col min="4" max="5" width="25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.7265625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="13.7265625" style="1"/>
+    <col min="6" max="6" width="24.77734375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="13.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -718,7 +721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -726,7 +729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -734,17 +737,25 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -758,14 +769,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C814E9C6-8B7D-4E61-A003-BF3C07F32BA3}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="25.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="25.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="25.1796875" style="1"/>
-    <col min="3" max="3" width="35.1796875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="25.1796875" style="1"/>
+    <col min="1" max="2" width="25.21875" style="1"/>
+    <col min="3" max="3" width="35.21875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="25.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,7 +796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -805,7 +816,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
@@ -825,7 +836,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -845,7 +856,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>54</v>
       </c>
@@ -865,7 +876,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -885,7 +896,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
@@ -914,14 +925,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D64820D-36BC-47E5-8B0C-19AD74EF9BDF}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="19.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="19.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.453125" style="1"/>
-    <col min="3" max="3" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="19.453125" style="1"/>
+    <col min="1" max="2" width="19.44140625" style="1"/>
+    <col min="3" max="3" width="22.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="19.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,7 +955,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -964,7 +975,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
@@ -984,7 +995,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1004,7 +1015,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>54</v>
       </c>
@@ -1029,12 +1040,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB6C1EA-3000-4832-B1CD-65BFF5950FD5}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="22.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="22.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="22.7265625" style="1"/>
+    <col min="1" max="16384" width="22.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -1059,7 +1070,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
@@ -1073,7 +1084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1086,15 +1097,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C5CD7-C2F0-4810-9B2B-3E979499F34C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="18.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="18.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.453125" style="1"/>
-    <col min="2" max="2" width="27.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="18.453125" style="1"/>
+    <col min="1" max="1" width="18.44140625" style="1"/>
+    <col min="2" max="2" width="27.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="18.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -1116,7 +1127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
@@ -1124,12 +1135,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>54</v>
       </c>
@@ -1145,12 +1156,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5A1E49-7B99-423D-9566-8E85E2D36AE6}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="16.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="16.54296875" style="1"/>
+    <col min="1" max="16384" width="16.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,7 +1196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -1202,7 +1213,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>

--- a/KatalonData/IWPBootstrapData/NormalizedSharedData.xlsx
+++ b/KatalonData/IWPBootstrapData/NormalizedSharedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0556D7F4-54AE-48D4-A141-6516AD04314D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E946AF49-BF29-47B3-90B0-C11279E9AE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
+    <workbookView xWindow="1956" yWindow="1404" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="5" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
   </bookViews>
   <sheets>
     <sheet name="NameData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
   <si>
     <t>ID</t>
   </si>
@@ -276,13 +276,28 @@
   </si>
   <si>
     <t>Carlos Jacinta</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>4118104714239507</t>
+  </si>
+  <si>
+    <t>Visa(Debit Card)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +316,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -338,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -347,6 +368,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,11 +790,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C814E9C6-8B7D-4E61-A003-BF3C07F32BA3}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="25.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="25.21875" style="1"/>
-    <col min="3" max="3" width="35.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="25.21875" style="1"/>
   </cols>
   <sheetData>
@@ -914,6 +936,26 @@
       </c>
       <c r="F7" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5A1E49-7B99-423D-9566-8E85E2D36AE6}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="16.5546875" style="1"/>
@@ -1218,6 +1260,17 @@
         <v>52</v>
       </c>
     </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
